--- a/output/yearly_population_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_82_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6852</v>
+        <v>7310</v>
       </c>
       <c r="C2" t="n">
-        <v>7112</v>
+        <v>6858</v>
       </c>
       <c r="D2" t="n">
-        <v>26008</v>
+        <v>31193</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5044</v>
+        <v>4975</v>
       </c>
       <c r="C3" t="n">
-        <v>7770</v>
+        <v>6169</v>
       </c>
       <c r="D3" t="n">
-        <v>14444</v>
+        <v>16549</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3340</v>
+        <v>3238</v>
       </c>
       <c r="C4" t="n">
-        <v>7047</v>
+        <v>4693</v>
       </c>
       <c r="D4" t="n">
-        <v>7349</v>
+        <v>7238</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2036</v>
+        <v>2159</v>
       </c>
       <c r="C5" t="n">
-        <v>5825</v>
+        <v>4382</v>
       </c>
       <c r="D5" t="n">
-        <v>3076</v>
+        <v>2632</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1095</v>
+        <v>1270</v>
       </c>
       <c r="C6" t="n">
-        <v>3233</v>
+        <v>3321</v>
       </c>
       <c r="D6" t="n">
-        <v>1315</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>477</v>
+        <v>597</v>
       </c>
       <c r="C7" t="n">
-        <v>1565</v>
+        <v>1932</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="C8" t="n">
-        <v>663</v>
+        <v>943</v>
       </c>
       <c r="D8" t="n">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>297</v>
+        <v>399</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -951,7 +951,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1052,7 +1052,7 @@
         <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8060</v>
+        <v>8566</v>
       </c>
       <c r="C2" t="n">
-        <v>8040</v>
+        <v>7631</v>
       </c>
       <c r="D2" t="n">
-        <v>30208</v>
+        <v>29937</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4825</v>
+        <v>4940</v>
       </c>
       <c r="C3" t="n">
-        <v>6592</v>
+        <v>5708</v>
       </c>
       <c r="D3" t="n">
-        <v>15184</v>
+        <v>17587</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3454</v>
+        <v>3378</v>
       </c>
       <c r="C4" t="n">
-        <v>7240</v>
+        <v>5289</v>
       </c>
       <c r="D4" t="n">
-        <v>8144</v>
+        <v>8378</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2276</v>
+        <v>2312</v>
       </c>
       <c r="C5" t="n">
-        <v>6199</v>
+        <v>4389</v>
       </c>
       <c r="D5" t="n">
-        <v>3609</v>
+        <v>3259</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1352</v>
+        <v>1497</v>
       </c>
       <c r="C6" t="n">
-        <v>4346</v>
+        <v>3757</v>
       </c>
       <c r="D6" t="n">
-        <v>1567</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>660</v>
+        <v>792</v>
       </c>
       <c r="C7" t="n">
-        <v>2268</v>
+        <v>2511</v>
       </c>
       <c r="D7" t="n">
-        <v>766</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>260</v>
+        <v>325</v>
       </c>
       <c r="C8" t="n">
-        <v>1042</v>
+        <v>1359</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="C9" t="n">
-        <v>441</v>
+        <v>613</v>
       </c>
       <c r="D9" t="n">
         <v>320</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>290</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D13" t="n">
         <v>126</v>
@@ -1262,7 +1262,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1363,7 +1363,7 @@
         <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8330</v>
+        <v>9892</v>
       </c>
       <c r="C2" t="n">
-        <v>9162</v>
+        <v>6758</v>
       </c>
       <c r="D2" t="n">
-        <v>41891</v>
+        <v>31515</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4975</v>
+        <v>5187</v>
       </c>
       <c r="C3" t="n">
-        <v>6373</v>
+        <v>5754</v>
       </c>
       <c r="D3" t="n">
-        <v>16015</v>
+        <v>17943</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3433</v>
+        <v>3399</v>
       </c>
       <c r="C4" t="n">
-        <v>6746</v>
+        <v>5305</v>
       </c>
       <c r="D4" t="n">
-        <v>8910</v>
+        <v>9368</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2417</v>
+        <v>2446</v>
       </c>
       <c r="C5" t="n">
-        <v>6499</v>
+        <v>4627</v>
       </c>
       <c r="D5" t="n">
-        <v>4074</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1552</v>
+        <v>1653</v>
       </c>
       <c r="C6" t="n">
-        <v>4995</v>
+        <v>3978</v>
       </c>
       <c r="D6" t="n">
-        <v>1805</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>826</v>
+        <v>954</v>
       </c>
       <c r="C7" t="n">
-        <v>3059</v>
+        <v>2973</v>
       </c>
       <c r="D7" t="n">
-        <v>868</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>360</v>
+        <v>441</v>
       </c>
       <c r="C8" t="n">
-        <v>1510</v>
+        <v>1785</v>
       </c>
       <c r="D8" t="n">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="C9" t="n">
-        <v>654</v>
+        <v>890</v>
       </c>
       <c r="D9" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>309</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1590,7 +1590,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1674,7 +1674,7 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7818</v>
+        <v>9117</v>
       </c>
       <c r="C2" t="n">
-        <v>6376</v>
+        <v>4649</v>
       </c>
       <c r="D2" t="n">
-        <v>34281</v>
+        <v>26073</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6019</v>
+        <v>6122</v>
       </c>
       <c r="C3" t="n">
-        <v>9920</v>
+        <v>8521</v>
       </c>
       <c r="D3" t="n">
-        <v>17342</v>
+        <v>19241</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2233</v>
+        <v>2260</v>
       </c>
       <c r="C4" t="n">
-        <v>9865</v>
+        <v>7293</v>
       </c>
       <c r="D4" t="n">
-        <v>8632</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1527</v>
       </c>
       <c r="C5" t="n">
-        <v>4895</v>
+        <v>3898</v>
       </c>
       <c r="D5" t="n">
-        <v>2863</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>763</v>
+        <v>881</v>
       </c>
       <c r="C6" t="n">
-        <v>2997</v>
+        <v>2913</v>
       </c>
       <c r="D6" t="n">
-        <v>850</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>332</v>
+        <v>407</v>
       </c>
       <c r="C7" t="n">
-        <v>1479</v>
+        <v>1749</v>
       </c>
       <c r="D7" t="n">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>153</v>
       </c>
       <c r="C8" t="n">
-        <v>640</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
-        <v>302</v>
+        <v>392</v>
       </c>
       <c r="D9" t="n">
         <v>245</v>
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1887,7 +1887,7 @@
         <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1971,7 +1971,7 @@
         <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4894</v>
+        <v>5453</v>
       </c>
       <c r="C2" t="n">
-        <v>2936</v>
+        <v>2999</v>
       </c>
       <c r="D2" t="n">
-        <v>23849</v>
+        <v>17916</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5875</v>
+        <v>6359</v>
       </c>
       <c r="C3" t="n">
-        <v>7597</v>
+        <v>6150</v>
       </c>
       <c r="D3" t="n">
-        <v>18813</v>
+        <v>19246</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3138</v>
+        <v>3236</v>
       </c>
       <c r="C4" t="n">
-        <v>9968</v>
+        <v>7987</v>
       </c>
       <c r="D4" t="n">
-        <v>9706</v>
+        <v>10127</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1609</v>
+        <v>1689</v>
       </c>
       <c r="C5" t="n">
-        <v>7032</v>
+        <v>5372</v>
       </c>
       <c r="D5" t="n">
-        <v>3578</v>
+        <v>3328</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>914</v>
+        <v>1042</v>
       </c>
       <c r="C6" t="n">
-        <v>3788</v>
+        <v>3393</v>
       </c>
       <c r="D6" t="n">
-        <v>1038</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>308</v>
+        <v>379</v>
       </c>
       <c r="C7" t="n">
-        <v>2010</v>
+        <v>2210</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>863</v>
+        <v>1133</v>
       </c>
       <c r="D8" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>439</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2184,7 +2184,7 @@
         <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4283</v>
+        <v>6523</v>
       </c>
       <c r="C2" t="n">
-        <v>4677</v>
+        <v>6084</v>
       </c>
       <c r="D2" t="n">
-        <v>23540</v>
+        <v>28044</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4647</v>
+        <v>5028</v>
       </c>
       <c r="C3" t="n">
-        <v>4820</v>
+        <v>4116</v>
       </c>
       <c r="D3" t="n">
-        <v>18233</v>
+        <v>17771</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3659</v>
+        <v>3930</v>
       </c>
       <c r="C4" t="n">
-        <v>8622</v>
+        <v>6998</v>
       </c>
       <c r="D4" t="n">
-        <v>10897</v>
+        <v>11307</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1982</v>
+        <v>2062</v>
       </c>
       <c r="C5" t="n">
-        <v>8306</v>
+        <v>6465</v>
       </c>
       <c r="D5" t="n">
-        <v>4410</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1103</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="n">
-        <v>5153</v>
+        <v>4267</v>
       </c>
       <c r="D6" t="n">
-        <v>1390</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>466</v>
+        <v>560</v>
       </c>
       <c r="C7" t="n">
-        <v>2778</v>
+        <v>2707</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="C8" t="n">
-        <v>1320</v>
+        <v>1576</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>705</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2495,7 +2495,7 @@
         <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2579,7 +2579,7 @@
         <v>57</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2601</v>
+        <v>3917</v>
       </c>
       <c r="C2" t="n">
-        <v>2221</v>
+        <v>2886</v>
       </c>
       <c r="D2" t="n">
-        <v>16430</v>
+        <v>19552</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4443</v>
+        <v>5188</v>
       </c>
       <c r="C3" t="n">
-        <v>4634</v>
+        <v>4642</v>
       </c>
       <c r="D3" t="n">
-        <v>18376</v>
+        <v>18441</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3977</v>
+        <v>4305</v>
       </c>
       <c r="C4" t="n">
-        <v>8148</v>
+        <v>6611</v>
       </c>
       <c r="D4" t="n">
-        <v>11764</v>
+        <v>12105</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2027</v>
+        <v>2137</v>
       </c>
       <c r="C5" t="n">
-        <v>9663</v>
+        <v>7557</v>
       </c>
       <c r="D5" t="n">
-        <v>4654</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>868</v>
+        <v>994</v>
       </c>
       <c r="C6" t="n">
-        <v>5941</v>
+        <v>5116</v>
       </c>
       <c r="D6" t="n">
-        <v>1356</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="C7" t="n">
-        <v>2702</v>
+        <v>2843</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>913</v>
+        <v>1169</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2792,7 +2792,7 @@
         <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3051</v>
+        <v>4863</v>
       </c>
       <c r="C2" t="n">
-        <v>6318</v>
+        <v>3104</v>
       </c>
       <c r="D2" t="n">
-        <v>14482</v>
+        <v>15808</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3179</v>
+        <v>3981</v>
       </c>
       <c r="C3" t="n">
-        <v>3183</v>
+        <v>3427</v>
       </c>
       <c r="D3" t="n">
-        <v>16921</v>
+        <v>17529</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3640</v>
+        <v>4107</v>
       </c>
       <c r="C4" t="n">
-        <v>6437</v>
+        <v>5610</v>
       </c>
       <c r="D4" t="n">
-        <v>12421</v>
+        <v>12710</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2478</v>
+        <v>2646</v>
       </c>
       <c r="C5" t="n">
-        <v>8900</v>
+        <v>7054</v>
       </c>
       <c r="D5" t="n">
-        <v>5536</v>
+        <v>5477</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1174</v>
+        <v>1282</v>
       </c>
       <c r="C6" t="n">
-        <v>7447</v>
+        <v>6127</v>
       </c>
       <c r="D6" t="n">
-        <v>1794</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>372</v>
       </c>
       <c r="C7" t="n">
-        <v>3965</v>
+        <v>3788</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1561</v>
+        <v>1782</v>
       </c>
       <c r="D8" t="n">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>470</v>
+        <v>576</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2224</v>
+        <v>3396</v>
       </c>
       <c r="C2" t="n">
-        <v>4883</v>
+        <v>1962</v>
       </c>
       <c r="D2" t="n">
-        <v>10697</v>
+        <v>11171</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2752</v>
+        <v>3735</v>
       </c>
       <c r="C3" t="n">
-        <v>3976</v>
+        <v>3000</v>
       </c>
       <c r="D3" t="n">
-        <v>15754</v>
+        <v>16368</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3235</v>
+        <v>3746</v>
       </c>
       <c r="C4" t="n">
-        <v>5207</v>
+        <v>4774</v>
       </c>
       <c r="D4" t="n">
-        <v>12724</v>
+        <v>13215</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2666</v>
+        <v>2896</v>
       </c>
       <c r="C5" t="n">
-        <v>8205</v>
+        <v>6597</v>
       </c>
       <c r="D5" t="n">
-        <v>6201</v>
+        <v>6126</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1385</v>
+        <v>1529</v>
       </c>
       <c r="C6" t="n">
-        <v>8182</v>
+        <v>6730</v>
       </c>
       <c r="D6" t="n">
-        <v>2095</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>4981</v>
+        <v>4559</v>
       </c>
       <c r="D7" t="n">
-        <v>747</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>2094</v>
+        <v>2298</v>
       </c>
       <c r="D8" t="n">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>525</v>
+        <v>652</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3849</v>
+        <v>5034</v>
       </c>
       <c r="C2" t="n">
-        <v>6868</v>
+        <v>2792</v>
       </c>
       <c r="D2" t="n">
-        <v>21456</v>
+        <v>14783</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2164</v>
+        <v>3041</v>
       </c>
       <c r="C3" t="n">
-        <v>3855</v>
+        <v>2303</v>
       </c>
       <c r="D3" t="n">
-        <v>14290</v>
+        <v>14696</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2694</v>
+        <v>3283</v>
       </c>
       <c r="C4" t="n">
-        <v>4590</v>
+        <v>3925</v>
       </c>
       <c r="D4" t="n">
-        <v>12622</v>
+        <v>13267</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2606</v>
+        <v>2899</v>
       </c>
       <c r="C5" t="n">
-        <v>6854</v>
+        <v>5724</v>
       </c>
       <c r="D5" t="n">
-        <v>6889</v>
+        <v>6892</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1673</v>
+        <v>1846</v>
       </c>
       <c r="C6" t="n">
-        <v>8123</v>
+        <v>6622</v>
       </c>
       <c r="D6" t="n">
-        <v>2580</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>540</v>
+        <v>627</v>
       </c>
       <c r="C7" t="n">
-        <v>6139</v>
+        <v>5365</v>
       </c>
       <c r="D7" t="n">
-        <v>897</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C8" t="n">
-        <v>3103</v>
+        <v>3117</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1021</v>
+        <v>1190</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="10">
@@ -3694,7 +3694,7 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
         <v>139</v>
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5038</v>
+        <v>7862</v>
       </c>
       <c r="C2" t="n">
-        <v>3804</v>
+        <v>9271</v>
       </c>
       <c r="D2" t="n">
-        <v>22381</v>
+        <v>14291</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2784</v>
+        <v>3603</v>
       </c>
       <c r="C2" t="n">
-        <v>4010</v>
+        <v>1608</v>
       </c>
       <c r="D2" t="n">
-        <v>15964</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3046</v>
+        <v>4096</v>
       </c>
       <c r="C3" t="n">
-        <v>4851</v>
+        <v>2593</v>
       </c>
       <c r="D3" t="n">
-        <v>15768</v>
+        <v>15945</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3759</v>
+        <v>4332</v>
       </c>
       <c r="C4" t="n">
-        <v>6976</v>
+        <v>5769</v>
       </c>
       <c r="D4" t="n">
-        <v>12922</v>
+        <v>13498</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1594</v>
+        <v>1786</v>
       </c>
       <c r="C5" t="n">
-        <v>10870</v>
+        <v>8928</v>
       </c>
       <c r="D5" t="n">
-        <v>6249</v>
+        <v>6199</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>498</v>
+        <v>579</v>
       </c>
       <c r="C6" t="n">
-        <v>7449</v>
+        <v>6555</v>
       </c>
       <c r="D6" t="n">
-        <v>2003</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>3054</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>1166</v>
       </c>
       <c r="D8" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="9">
@@ -4302,7 +4302,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>343</v>
       </c>
       <c r="D9" t="n">
         <v>181</v>
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
         <v>136</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7019</v>
+        <v>7722</v>
       </c>
       <c r="C2" t="n">
-        <v>6010</v>
+        <v>5061</v>
       </c>
       <c r="D2" t="n">
-        <v>19819</v>
+        <v>14798</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2141</v>
+        <v>3339</v>
       </c>
       <c r="C3" t="n">
-        <v>1917</v>
+        <v>4672</v>
       </c>
       <c r="D3" t="n">
-        <v>4399</v>
+        <v>3040</v>
       </c>
     </row>
     <row r="4">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>6934</v>
       </c>
       <c r="C2" t="n">
-        <v>6456</v>
+        <v>6326</v>
       </c>
       <c r="D2" t="n">
-        <v>19611</v>
+        <v>18463</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3757</v>
+        <v>4544</v>
       </c>
       <c r="C3" t="n">
-        <v>3650</v>
+        <v>4218</v>
       </c>
       <c r="D3" t="n">
-        <v>6665</v>
+        <v>4791</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>964</v>
+        <v>1485</v>
       </c>
       <c r="C4" t="n">
-        <v>1168</v>
+        <v>2781</v>
       </c>
       <c r="D4" t="n">
-        <v>2068</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5937</v>
+        <v>6813</v>
       </c>
       <c r="C2" t="n">
-        <v>7801</v>
+        <v>8770</v>
       </c>
       <c r="D2" t="n">
-        <v>20238</v>
+        <v>15594</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3659</v>
+        <v>4692</v>
       </c>
       <c r="C3" t="n">
-        <v>4483</v>
+        <v>4635</v>
       </c>
       <c r="D3" t="n">
-        <v>8256</v>
+        <v>6633</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1995</v>
+        <v>2567</v>
       </c>
       <c r="C4" t="n">
-        <v>2549</v>
+        <v>3496</v>
       </c>
       <c r="D4" t="n">
-        <v>2887</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>456</v>
+        <v>657</v>
       </c>
       <c r="C5" t="n">
-        <v>734</v>
+        <v>1618</v>
       </c>
       <c r="D5" t="n">
-        <v>1308</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,10 +5207,10 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>126</v>
       </c>
       <c r="C8" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5249,7 +5249,7 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
         <v>346</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5336,7 +5336,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6946</v>
+        <v>6241</v>
       </c>
       <c r="C2" t="n">
-        <v>12411</v>
+        <v>8303</v>
       </c>
       <c r="D2" t="n">
-        <v>21464</v>
+        <v>27253</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3884</v>
+        <v>4665</v>
       </c>
       <c r="C3" t="n">
-        <v>5388</v>
+        <v>5886</v>
       </c>
       <c r="D3" t="n">
-        <v>9496</v>
+        <v>7528</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2400</v>
+        <v>3041</v>
       </c>
       <c r="C4" t="n">
-        <v>3511</v>
+        <v>4035</v>
       </c>
       <c r="D4" t="n">
-        <v>3778</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1000</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="n">
-        <v>1677</v>
+        <v>2557</v>
       </c>
       <c r="D5" t="n">
-        <v>1528</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>264</v>
+        <v>340</v>
       </c>
       <c r="C6" t="n">
-        <v>517</v>
+        <v>954</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7496</v>
+        <v>6846</v>
       </c>
       <c r="C2" t="n">
-        <v>12564</v>
+        <v>5713</v>
       </c>
       <c r="D2" t="n">
-        <v>29209</v>
+        <v>34722</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3896</v>
+        <v>3987</v>
       </c>
       <c r="C3" t="n">
-        <v>7353</v>
+        <v>5818</v>
       </c>
       <c r="D3" t="n">
-        <v>10016</v>
+        <v>9403</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1936</v>
+        <v>2360</v>
       </c>
       <c r="C4" t="n">
-        <v>3697</v>
+        <v>4091</v>
       </c>
       <c r="D4" t="n">
-        <v>4103</v>
+        <v>3277</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>887</v>
+        <v>1128</v>
       </c>
       <c r="C5" t="n">
-        <v>1936</v>
+        <v>2425</v>
       </c>
       <c r="D5" t="n">
-        <v>1503</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>296</v>
+        <v>392</v>
       </c>
       <c r="C6" t="n">
-        <v>742</v>
+        <v>1169</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>274</v>
+        <v>413</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5955,10 +5955,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7113</v>
+        <v>6933</v>
       </c>
       <c r="C2" t="n">
-        <v>7662</v>
+        <v>5875</v>
       </c>
       <c r="D2" t="n">
-        <v>23905</v>
+        <v>29002</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4738</v>
+        <v>4478</v>
       </c>
       <c r="C3" t="n">
-        <v>8944</v>
+        <v>4956</v>
       </c>
       <c r="D3" t="n">
-        <v>12503</v>
+        <v>12964</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>2771</v>
       </c>
       <c r="C4" t="n">
-        <v>5831</v>
+        <v>4994</v>
       </c>
       <c r="D4" t="n">
-        <v>5130</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1259</v>
+        <v>1536</v>
       </c>
       <c r="C5" t="n">
-        <v>2926</v>
+        <v>3350</v>
       </c>
       <c r="D5" t="n">
-        <v>1981</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>702</v>
       </c>
       <c r="C6" t="n">
-        <v>1409</v>
+        <v>1866</v>
       </c>
       <c r="D6" t="n">
-        <v>929</v>
+        <v>873</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>175</v>
+        <v>221</v>
       </c>
       <c r="C7" t="n">
-        <v>532</v>
+        <v>835</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="D8" t="n">
         <v>385</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6213,7 +6213,7 @@
         <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7589</v>
+        <v>7837</v>
       </c>
       <c r="C2" t="n">
-        <v>10707</v>
+        <v>9524</v>
       </c>
       <c r="D2" t="n">
-        <v>26906</v>
+        <v>35134</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4847</v>
+        <v>4646</v>
       </c>
       <c r="C3" t="n">
-        <v>7161</v>
+        <v>4724</v>
       </c>
       <c r="D3" t="n">
-        <v>13427</v>
+        <v>14596</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3137</v>
+        <v>3082</v>
       </c>
       <c r="C4" t="n">
-        <v>7387</v>
+        <v>4868</v>
       </c>
       <c r="D4" t="n">
-        <v>6389</v>
+        <v>5919</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1656</v>
+        <v>1890</v>
       </c>
       <c r="C5" t="n">
-        <v>4454</v>
+        <v>4164</v>
       </c>
       <c r="D5" t="n">
-        <v>2476</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>816</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>2193</v>
+        <v>2596</v>
       </c>
       <c r="D6" t="n">
-        <v>1107</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>403</v>
       </c>
       <c r="C7" t="n">
-        <v>987</v>
+        <v>1370</v>
       </c>
       <c r="D7" t="n">
-        <v>616</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>388</v>
+        <v>579</v>
       </c>
       <c r="D8" t="n">
         <v>405</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6650,7 +6650,7 @@
         <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_82_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7310</v>
+        <v>5837</v>
       </c>
       <c r="C2" t="n">
-        <v>6858</v>
+        <v>7598</v>
       </c>
       <c r="D2" t="n">
-        <v>31193</v>
+        <v>22197</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4975</v>
+        <v>3729</v>
       </c>
       <c r="C3" t="n">
-        <v>6169</v>
+        <v>3070</v>
       </c>
       <c r="D3" t="n">
-        <v>16549</v>
+        <v>13377</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3238</v>
+        <v>2878</v>
       </c>
       <c r="C4" t="n">
-        <v>4693</v>
+        <v>3180</v>
       </c>
       <c r="D4" t="n">
-        <v>7238</v>
+        <v>5597</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2159</v>
+        <v>1978</v>
       </c>
       <c r="C5" t="n">
-        <v>4382</v>
+        <v>3409</v>
       </c>
       <c r="D5" t="n">
-        <v>2632</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1270</v>
+        <v>1109</v>
       </c>
       <c r="C6" t="n">
-        <v>3321</v>
+        <v>3269</v>
       </c>
       <c r="D6" t="n">
-        <v>1151</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>597</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>1932</v>
+        <v>2475</v>
       </c>
       <c r="D7" t="n">
-        <v>650</v>
+        <v>638</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>943</v>
+        <v>1288</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>399</v>
+        <v>499</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -937,7 +937,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
         <v>123</v>
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8566</v>
+        <v>7035</v>
       </c>
       <c r="C2" t="n">
-        <v>7631</v>
+        <v>7808</v>
       </c>
       <c r="D2" t="n">
-        <v>29937</v>
+        <v>19570</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4940</v>
+        <v>3803</v>
       </c>
       <c r="C3" t="n">
-        <v>5708</v>
+        <v>4512</v>
       </c>
       <c r="D3" t="n">
-        <v>17587</v>
+        <v>13677</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3378</v>
+        <v>2805</v>
       </c>
       <c r="C4" t="n">
-        <v>5289</v>
+        <v>3030</v>
       </c>
       <c r="D4" t="n">
-        <v>8378</v>
+        <v>6696</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2312</v>
+        <v>2095</v>
       </c>
       <c r="C5" t="n">
-        <v>4389</v>
+        <v>3230</v>
       </c>
       <c r="D5" t="n">
-        <v>3259</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1497</v>
+        <v>1348</v>
       </c>
       <c r="C6" t="n">
-        <v>3757</v>
+        <v>3268</v>
       </c>
       <c r="D6" t="n">
-        <v>1337</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>792</v>
+        <v>689</v>
       </c>
       <c r="C7" t="n">
-        <v>2511</v>
+        <v>2831</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>681</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="C8" t="n">
-        <v>1359</v>
+        <v>1786</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>613</v>
+        <v>831</v>
       </c>
       <c r="D9" t="n">
         <v>320</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>139</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9892</v>
+        <v>7983</v>
       </c>
       <c r="C2" t="n">
-        <v>6758</v>
+        <v>8160</v>
       </c>
       <c r="D2" t="n">
-        <v>31515</v>
+        <v>23136</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5187</v>
+        <v>4147</v>
       </c>
       <c r="C3" t="n">
-        <v>5754</v>
+        <v>5212</v>
       </c>
       <c r="D3" t="n">
-        <v>17943</v>
+        <v>13534</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3399</v>
+        <v>2736</v>
       </c>
       <c r="C4" t="n">
-        <v>5305</v>
+        <v>3592</v>
       </c>
       <c r="D4" t="n">
-        <v>9368</v>
+        <v>7564</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2446</v>
+        <v>2123</v>
       </c>
       <c r="C5" t="n">
-        <v>4627</v>
+        <v>3076</v>
       </c>
       <c r="D5" t="n">
-        <v>3897</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1653</v>
+        <v>1506</v>
       </c>
       <c r="C6" t="n">
-        <v>3978</v>
+        <v>3190</v>
       </c>
       <c r="D6" t="n">
-        <v>1564</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>954</v>
+        <v>856</v>
       </c>
       <c r="C7" t="n">
-        <v>2973</v>
+        <v>2981</v>
       </c>
       <c r="D7" t="n">
-        <v>794</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>441</v>
+        <v>389</v>
       </c>
       <c r="C8" t="n">
-        <v>1785</v>
+        <v>2205</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="C9" t="n">
-        <v>890</v>
+        <v>1187</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>520</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9117</v>
+        <v>7279</v>
       </c>
       <c r="C2" t="n">
-        <v>4649</v>
+        <v>5483</v>
       </c>
       <c r="D2" t="n">
-        <v>26073</v>
+        <v>19028</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6122</v>
+        <v>4981</v>
       </c>
       <c r="C3" t="n">
-        <v>8521</v>
+        <v>7496</v>
       </c>
       <c r="D3" t="n">
-        <v>19241</v>
+        <v>14723</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2260</v>
+        <v>1961</v>
       </c>
       <c r="C4" t="n">
-        <v>7293</v>
+        <v>4952</v>
       </c>
       <c r="D4" t="n">
-        <v>8809</v>
+        <v>7094</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1527</v>
+        <v>1391</v>
       </c>
       <c r="C5" t="n">
-        <v>3898</v>
+        <v>3126</v>
       </c>
       <c r="D5" t="n">
-        <v>2580</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>881</v>
+        <v>790</v>
       </c>
       <c r="C6" t="n">
-        <v>2913</v>
+        <v>2921</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>407</v>
+        <v>359</v>
       </c>
       <c r="C7" t="n">
-        <v>1749</v>
+        <v>2160</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C8" t="n">
-        <v>872</v>
+        <v>1163</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>392</v>
+        <v>509</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5453</v>
+        <v>4515</v>
       </c>
       <c r="C2" t="n">
-        <v>2999</v>
+        <v>2511</v>
       </c>
       <c r="D2" t="n">
-        <v>17916</v>
+        <v>12893</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6359</v>
+        <v>5145</v>
       </c>
       <c r="C3" t="n">
-        <v>6150</v>
+        <v>5950</v>
       </c>
       <c r="D3" t="n">
-        <v>19246</v>
+        <v>14460</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3236</v>
+        <v>2721</v>
       </c>
       <c r="C4" t="n">
-        <v>7987</v>
+        <v>6235</v>
       </c>
       <c r="D4" t="n">
-        <v>10127</v>
+        <v>8186</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1689</v>
+        <v>1539</v>
       </c>
       <c r="C5" t="n">
-        <v>5372</v>
+        <v>3934</v>
       </c>
       <c r="D5" t="n">
-        <v>3328</v>
+        <v>2770</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1042</v>
+        <v>946</v>
       </c>
       <c r="C6" t="n">
-        <v>3393</v>
+        <v>3171</v>
       </c>
       <c r="D6" t="n">
-        <v>964</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>379</v>
+        <v>335</v>
       </c>
       <c r="C7" t="n">
-        <v>2210</v>
+        <v>2558</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C8" t="n">
-        <v>1133</v>
+        <v>1488</v>
       </c>
       <c r="D8" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>439</v>
+        <v>573</v>
       </c>
       <c r="D9" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,10 +2164,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D12" t="n">
         <v>131</v>
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6523</v>
+        <v>5092</v>
       </c>
       <c r="C2" t="n">
-        <v>6084</v>
+        <v>10597</v>
       </c>
       <c r="D2" t="n">
-        <v>28044</v>
+        <v>14259</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5028</v>
+        <v>4131</v>
       </c>
       <c r="C3" t="n">
-        <v>4116</v>
+        <v>3806</v>
       </c>
       <c r="D3" t="n">
-        <v>17771</v>
+        <v>13239</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3930</v>
+        <v>3232</v>
       </c>
       <c r="C4" t="n">
-        <v>6998</v>
+        <v>5963</v>
       </c>
       <c r="D4" t="n">
-        <v>11307</v>
+        <v>9021</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2062</v>
+        <v>1823</v>
       </c>
       <c r="C5" t="n">
-        <v>6465</v>
+        <v>4956</v>
       </c>
       <c r="D5" t="n">
-        <v>4271</v>
+        <v>3569</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1200</v>
+        <v>1111</v>
       </c>
       <c r="C6" t="n">
-        <v>4267</v>
+        <v>3521</v>
       </c>
       <c r="D6" t="n">
-        <v>1291</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>560</v>
+        <v>505</v>
       </c>
       <c r="C7" t="n">
-        <v>2707</v>
+        <v>2852</v>
       </c>
       <c r="D7" t="n">
-        <v>571</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="C8" t="n">
-        <v>1576</v>
+        <v>1942</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>705</v>
+        <v>928</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>366</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>133</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3917</v>
+        <v>2989</v>
       </c>
       <c r="C2" t="n">
-        <v>2886</v>
+        <v>4898</v>
       </c>
       <c r="D2" t="n">
-        <v>19552</v>
+        <v>9836</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5188</v>
+        <v>4213</v>
       </c>
       <c r="C3" t="n">
-        <v>4642</v>
+        <v>5983</v>
       </c>
       <c r="D3" t="n">
-        <v>18441</v>
+        <v>13035</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4305</v>
+        <v>3601</v>
       </c>
       <c r="C4" t="n">
-        <v>6611</v>
+        <v>5723</v>
       </c>
       <c r="D4" t="n">
-        <v>12105</v>
+        <v>9584</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2137</v>
+        <v>1929</v>
       </c>
       <c r="C5" t="n">
-        <v>7557</v>
+        <v>5879</v>
       </c>
       <c r="D5" t="n">
-        <v>4523</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>994</v>
+        <v>928</v>
       </c>
       <c r="C6" t="n">
-        <v>5116</v>
+        <v>4512</v>
       </c>
       <c r="D6" t="n">
-        <v>1265</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C7" t="n">
-        <v>2843</v>
+        <v>3222</v>
       </c>
       <c r="D7" t="n">
-        <v>572</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1169</v>
+        <v>1518</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>358</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>130</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4863</v>
+        <v>3991</v>
       </c>
       <c r="C2" t="n">
-        <v>3104</v>
+        <v>8070</v>
       </c>
       <c r="D2" t="n">
-        <v>15808</v>
+        <v>10474</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3981</v>
+        <v>3122</v>
       </c>
       <c r="C3" t="n">
-        <v>3427</v>
+        <v>4851</v>
       </c>
       <c r="D3" t="n">
-        <v>17529</v>
+        <v>11802</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4107</v>
+        <v>3404</v>
       </c>
       <c r="C4" t="n">
-        <v>5610</v>
+        <v>5786</v>
       </c>
       <c r="D4" t="n">
-        <v>12710</v>
+        <v>9855</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2646</v>
+        <v>2329</v>
       </c>
       <c r="C5" t="n">
-        <v>7054</v>
+        <v>5741</v>
       </c>
       <c r="D5" t="n">
-        <v>5477</v>
+        <v>4642</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1282</v>
+        <v>1205</v>
       </c>
       <c r="C6" t="n">
-        <v>6127</v>
+        <v>5104</v>
       </c>
       <c r="D6" t="n">
-        <v>1686</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="C7" t="n">
-        <v>3788</v>
+        <v>3814</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>1782</v>
+        <v>2181</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>576</v>
+        <v>754</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D11" t="n">
         <v>134</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3396</v>
+        <v>2755</v>
       </c>
       <c r="C2" t="n">
-        <v>1962</v>
+        <v>4174</v>
       </c>
       <c r="D2" t="n">
-        <v>11171</v>
+        <v>7461</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3735</v>
+        <v>2990</v>
       </c>
       <c r="C3" t="n">
-        <v>3000</v>
+        <v>5642</v>
       </c>
       <c r="D3" t="n">
-        <v>16368</v>
+        <v>11084</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3746</v>
+        <v>3055</v>
       </c>
       <c r="C4" t="n">
-        <v>4774</v>
+        <v>5437</v>
       </c>
       <c r="D4" t="n">
-        <v>13215</v>
+        <v>9911</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2896</v>
+        <v>2546</v>
       </c>
       <c r="C5" t="n">
-        <v>6597</v>
+        <v>5803</v>
       </c>
       <c r="D5" t="n">
-        <v>6126</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1529</v>
+        <v>1415</v>
       </c>
       <c r="C6" t="n">
-        <v>6730</v>
+        <v>5575</v>
       </c>
       <c r="D6" t="n">
-        <v>2042</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C7" t="n">
-        <v>4559</v>
+        <v>4365</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2298</v>
+        <v>2704</v>
       </c>
       <c r="D8" t="n">
-        <v>407</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>652</v>
+        <v>892</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5034</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="n">
-        <v>2792</v>
+        <v>6812</v>
       </c>
       <c r="D2" t="n">
-        <v>14783</v>
+        <v>8653</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3041</v>
+        <v>2442</v>
       </c>
       <c r="C3" t="n">
-        <v>2303</v>
+        <v>4460</v>
       </c>
       <c r="D3" t="n">
-        <v>14696</v>
+        <v>9999</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3283</v>
+        <v>2634</v>
       </c>
       <c r="C4" t="n">
-        <v>3925</v>
+        <v>5414</v>
       </c>
       <c r="D4" t="n">
-        <v>13267</v>
+        <v>9683</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2899</v>
+        <v>2510</v>
       </c>
       <c r="C5" t="n">
-        <v>5724</v>
+        <v>5527</v>
       </c>
       <c r="D5" t="n">
-        <v>6892</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1846</v>
+        <v>1668</v>
       </c>
       <c r="C6" t="n">
-        <v>6622</v>
+        <v>5617</v>
       </c>
       <c r="D6" t="n">
-        <v>2525</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C7" t="n">
-        <v>5365</v>
+        <v>4880</v>
       </c>
       <c r="D7" t="n">
-        <v>880</v>
+        <v>840</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>3117</v>
+        <v>3305</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>1190</v>
+        <v>1521</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>350</v>
+        <v>452</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
         <v>37</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7862</v>
+        <v>5736</v>
       </c>
       <c r="C2" t="n">
-        <v>9271</v>
+        <v>13522</v>
       </c>
       <c r="D2" t="n">
-        <v>14291</v>
+        <v>6178</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3603</v>
+        <v>2617</v>
       </c>
       <c r="C2" t="n">
-        <v>1608</v>
+        <v>3814</v>
       </c>
       <c r="D2" t="n">
-        <v>10880</v>
+        <v>6368</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4096</v>
+        <v>3243</v>
       </c>
       <c r="C3" t="n">
-        <v>2593</v>
+        <v>5402</v>
       </c>
       <c r="D3" t="n">
-        <v>15945</v>
+        <v>10710</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4332</v>
+        <v>3662</v>
       </c>
       <c r="C4" t="n">
-        <v>5769</v>
+        <v>7356</v>
       </c>
       <c r="D4" t="n">
-        <v>13498</v>
+        <v>10053</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1786</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="n">
-        <v>8928</v>
+        <v>7954</v>
       </c>
       <c r="D5" t="n">
-        <v>6199</v>
+        <v>5267</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C6" t="n">
-        <v>6555</v>
+        <v>5993</v>
       </c>
       <c r="D6" t="n">
-        <v>1987</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>3054</v>
+        <v>3238</v>
       </c>
       <c r="D7" t="n">
-        <v>541</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>1166</v>
+        <v>1490</v>
       </c>
       <c r="D8" t="n">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="D10" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
         <v>36</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7722</v>
+        <v>6732</v>
       </c>
       <c r="C2" t="n">
-        <v>5061</v>
+        <v>6729</v>
       </c>
       <c r="D2" t="n">
-        <v>14798</v>
+        <v>13789</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3339</v>
+        <v>2437</v>
       </c>
       <c r="C3" t="n">
-        <v>4672</v>
+        <v>6815</v>
       </c>
       <c r="D3" t="n">
-        <v>3040</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6934</v>
+        <v>5880</v>
       </c>
       <c r="C2" t="n">
-        <v>6326</v>
+        <v>8416</v>
       </c>
       <c r="D2" t="n">
-        <v>18463</v>
+        <v>12201</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4544</v>
+        <v>3764</v>
       </c>
       <c r="C3" t="n">
-        <v>4218</v>
+        <v>5835</v>
       </c>
       <c r="D3" t="n">
-        <v>4791</v>
+        <v>3588</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1485</v>
+        <v>1093</v>
       </c>
       <c r="C4" t="n">
-        <v>2781</v>
+        <v>4036</v>
       </c>
       <c r="D4" t="n">
-        <v>1794</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4896,7 +4896,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6813</v>
+        <v>6394</v>
       </c>
       <c r="C2" t="n">
-        <v>8770</v>
+        <v>4562</v>
       </c>
       <c r="D2" t="n">
-        <v>15594</v>
+        <v>14665</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4692</v>
+        <v>3940</v>
       </c>
       <c r="C3" t="n">
-        <v>4635</v>
+        <v>6257</v>
       </c>
       <c r="D3" t="n">
-        <v>6633</v>
+        <v>4707</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2567</v>
+        <v>2064</v>
       </c>
       <c r="C4" t="n">
-        <v>3496</v>
+        <v>4914</v>
       </c>
       <c r="D4" t="n">
-        <v>2314</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>657</v>
+        <v>500</v>
       </c>
       <c r="C5" t="n">
-        <v>1618</v>
+        <v>2304</v>
       </c>
       <c r="D5" t="n">
-        <v>1258</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5232,7 +5232,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C9" t="n">
         <v>268</v>
@@ -5263,7 +5263,7 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6241</v>
+        <v>6050</v>
       </c>
       <c r="C2" t="n">
-        <v>8303</v>
+        <v>2812</v>
       </c>
       <c r="D2" t="n">
-        <v>27253</v>
+        <v>20410</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4665</v>
+        <v>4165</v>
       </c>
       <c r="C3" t="n">
-        <v>5886</v>
+        <v>4710</v>
       </c>
       <c r="D3" t="n">
-        <v>7528</v>
+        <v>5889</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3041</v>
+        <v>2511</v>
       </c>
       <c r="C4" t="n">
-        <v>4035</v>
+        <v>5473</v>
       </c>
       <c r="D4" t="n">
-        <v>3031</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1330</v>
+        <v>1054</v>
       </c>
       <c r="C5" t="n">
-        <v>2557</v>
+        <v>3609</v>
       </c>
       <c r="D5" t="n">
-        <v>1390</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>340</v>
+        <v>277</v>
       </c>
       <c r="C6" t="n">
-        <v>954</v>
+        <v>1299</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>947</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D7" t="n">
         <v>660</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D8" t="n">
         <v>478</v>
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5574,7 +5574,7 @@
         <v>49</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6846</v>
+        <v>6569</v>
       </c>
       <c r="C2" t="n">
-        <v>5713</v>
+        <v>5305</v>
       </c>
       <c r="D2" t="n">
-        <v>34722</v>
+        <v>23762</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3987</v>
+        <v>3725</v>
       </c>
       <c r="C3" t="n">
-        <v>5818</v>
+        <v>3081</v>
       </c>
       <c r="D3" t="n">
-        <v>9403</v>
+        <v>7226</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2360</v>
+        <v>2041</v>
       </c>
       <c r="C4" t="n">
-        <v>4091</v>
+        <v>4097</v>
       </c>
       <c r="D4" t="n">
-        <v>3277</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1128</v>
+        <v>917</v>
       </c>
       <c r="C5" t="n">
-        <v>2425</v>
+        <v>3339</v>
       </c>
       <c r="D5" t="n">
-        <v>1310</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>392</v>
+        <v>313</v>
       </c>
       <c r="C6" t="n">
-        <v>1169</v>
+        <v>1643</v>
       </c>
       <c r="D6" t="n">
-        <v>783</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>413</v>
+        <v>511</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
         <v>223</v>
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
         <v>273</v>
@@ -5882,7 +5882,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
         <v>114</v>
@@ -5899,7 +5899,7 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5955,7 +5955,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>64</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6933</v>
+        <v>5212</v>
       </c>
       <c r="C2" t="n">
-        <v>5875</v>
+        <v>3381</v>
       </c>
       <c r="D2" t="n">
-        <v>29002</v>
+        <v>30418</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4478</v>
+        <v>4256</v>
       </c>
       <c r="C3" t="n">
-        <v>4956</v>
+        <v>3768</v>
       </c>
       <c r="D3" t="n">
-        <v>12964</v>
+        <v>9472</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2771</v>
+        <v>2502</v>
       </c>
       <c r="C4" t="n">
-        <v>4994</v>
+        <v>3397</v>
       </c>
       <c r="D4" t="n">
-        <v>4412</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1536</v>
+        <v>1318</v>
       </c>
       <c r="C5" t="n">
-        <v>3350</v>
+        <v>3713</v>
       </c>
       <c r="D5" t="n">
-        <v>1635</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>702</v>
+        <v>568</v>
       </c>
       <c r="C6" t="n">
-        <v>1866</v>
+        <v>2583</v>
       </c>
       <c r="D6" t="n">
-        <v>873</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="C7" t="n">
-        <v>835</v>
+        <v>1143</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D9" t="n">
         <v>285</v>
@@ -6182,7 +6182,7 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
         <v>235</v>
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6255,7 +6255,7 @@
         <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7837</v>
+        <v>5294</v>
       </c>
       <c r="C2" t="n">
-        <v>9524</v>
+        <v>3952</v>
       </c>
       <c r="D2" t="n">
-        <v>35134</v>
+        <v>26531</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4646</v>
+        <v>3892</v>
       </c>
       <c r="C3" t="n">
-        <v>4724</v>
+        <v>3088</v>
       </c>
       <c r="D3" t="n">
-        <v>14596</v>
+        <v>12141</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3082</v>
+        <v>2906</v>
       </c>
       <c r="C4" t="n">
-        <v>4868</v>
+        <v>3500</v>
       </c>
       <c r="D4" t="n">
-        <v>5919</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1890</v>
+        <v>1659</v>
       </c>
       <c r="C5" t="n">
-        <v>4164</v>
+        <v>3462</v>
       </c>
       <c r="D5" t="n">
-        <v>2091</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>854</v>
       </c>
       <c r="C6" t="n">
-        <v>2596</v>
+        <v>3150</v>
       </c>
       <c r="D6" t="n">
-        <v>984</v>
+        <v>914</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>403</v>
+        <v>326</v>
       </c>
       <c r="C7" t="n">
-        <v>1370</v>
+        <v>1890</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>579</v>
+        <v>755</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="D9" t="n">
         <v>298</v>
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6535,7 +6535,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6566,7 +6566,7 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_82_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_82_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5837</v>
+        <v>772</v>
       </c>
       <c r="C2" t="n">
-        <v>7598</v>
+        <v>3345</v>
       </c>
       <c r="D2" t="n">
-        <v>22197</v>
+        <v>13175</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3729</v>
+        <v>1490</v>
       </c>
       <c r="C3" t="n">
-        <v>3070</v>
+        <v>8318</v>
       </c>
       <c r="D3" t="n">
-        <v>13377</v>
+        <v>10901</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2878</v>
+        <v>1084</v>
       </c>
       <c r="C4" t="n">
-        <v>3180</v>
+        <v>9406</v>
       </c>
       <c r="D4" t="n">
-        <v>5597</v>
+        <v>5274</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1978</v>
+        <v>532</v>
       </c>
       <c r="C5" t="n">
-        <v>3409</v>
+        <v>5110</v>
       </c>
       <c r="D5" t="n">
-        <v>2117</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1109</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>3269</v>
+        <v>2033</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>98</v>
       </c>
       <c r="C7" t="n">
-        <v>2475</v>
+        <v>785</v>
       </c>
       <c r="D7" t="n">
-        <v>638</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1288</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>424</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>499</v>
+        <v>286</v>
       </c>
       <c r="D9" t="n">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7035</v>
+        <v>1714</v>
       </c>
       <c r="C2" t="n">
-        <v>7808</v>
+        <v>7433</v>
       </c>
       <c r="D2" t="n">
-        <v>19570</v>
+        <v>12894</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3803</v>
+        <v>975</v>
       </c>
       <c r="C3" t="n">
-        <v>4512</v>
+        <v>4985</v>
       </c>
       <c r="D3" t="n">
-        <v>13677</v>
+        <v>10479</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2805</v>
+        <v>1110</v>
       </c>
       <c r="C4" t="n">
-        <v>3030</v>
+        <v>8705</v>
       </c>
       <c r="D4" t="n">
-        <v>6696</v>
+        <v>6140</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2095</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>3230</v>
+        <v>7230</v>
       </c>
       <c r="D5" t="n">
-        <v>2566</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1348</v>
+        <v>334</v>
       </c>
       <c r="C6" t="n">
-        <v>3268</v>
+        <v>3567</v>
       </c>
       <c r="D6" t="n">
-        <v>1173</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>689</v>
+        <v>139</v>
       </c>
       <c r="C7" t="n">
-        <v>2831</v>
+        <v>1391</v>
       </c>
       <c r="D7" t="n">
-        <v>681</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>1786</v>
+        <v>555</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>831</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>336</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7983</v>
+        <v>910</v>
       </c>
       <c r="C2" t="n">
-        <v>8160</v>
+        <v>3136</v>
       </c>
       <c r="D2" t="n">
-        <v>23136</v>
+        <v>8837</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4147</v>
+        <v>1139</v>
       </c>
       <c r="C3" t="n">
-        <v>5212</v>
+        <v>5725</v>
       </c>
       <c r="D3" t="n">
-        <v>13534</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2736</v>
+        <v>1205</v>
       </c>
       <c r="C4" t="n">
-        <v>3592</v>
+        <v>7931</v>
       </c>
       <c r="D4" t="n">
-        <v>7564</v>
+        <v>6706</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2123</v>
+        <v>697</v>
       </c>
       <c r="C5" t="n">
-        <v>3076</v>
+        <v>8517</v>
       </c>
       <c r="D5" t="n">
-        <v>3058</v>
+        <v>2767</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1506</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>3190</v>
+        <v>4627</v>
       </c>
       <c r="D6" t="n">
-        <v>1358</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>856</v>
+        <v>71</v>
       </c>
       <c r="C7" t="n">
-        <v>2981</v>
+        <v>1343</v>
       </c>
       <c r="D7" t="n">
-        <v>734</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>389</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2205</v>
+        <v>506</v>
       </c>
       <c r="D8" t="n">
-        <v>477</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1187</v>
+        <v>239</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>520</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>240</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7279</v>
+        <v>903</v>
       </c>
       <c r="C2" t="n">
-        <v>5483</v>
+        <v>5143</v>
       </c>
       <c r="D2" t="n">
-        <v>19028</v>
+        <v>10583</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4981</v>
+        <v>871</v>
       </c>
       <c r="C3" t="n">
-        <v>7496</v>
+        <v>3878</v>
       </c>
       <c r="D3" t="n">
-        <v>14723</v>
+        <v>9608</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1961</v>
+        <v>1042</v>
       </c>
       <c r="C4" t="n">
-        <v>4952</v>
+        <v>6677</v>
       </c>
       <c r="D4" t="n">
-        <v>7094</v>
+        <v>7157</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1391</v>
+        <v>822</v>
       </c>
       <c r="C5" t="n">
-        <v>3126</v>
+        <v>8129</v>
       </c>
       <c r="D5" t="n">
-        <v>2182</v>
+        <v>3325</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>790</v>
+        <v>407</v>
       </c>
       <c r="C6" t="n">
-        <v>2921</v>
+        <v>6500</v>
       </c>
       <c r="D6" t="n">
-        <v>719</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>359</v>
+        <v>128</v>
       </c>
       <c r="C7" t="n">
-        <v>2160</v>
+        <v>2817</v>
       </c>
       <c r="D7" t="n">
-        <v>467</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1163</v>
+        <v>852</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>509</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4515</v>
+        <v>611</v>
       </c>
       <c r="C2" t="n">
-        <v>2511</v>
+        <v>3476</v>
       </c>
       <c r="D2" t="n">
-        <v>12893</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5145</v>
+        <v>771</v>
       </c>
       <c r="C3" t="n">
-        <v>5950</v>
+        <v>3993</v>
       </c>
       <c r="D3" t="n">
-        <v>14460</v>
+        <v>9279</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2721</v>
+        <v>907</v>
       </c>
       <c r="C4" t="n">
-        <v>6235</v>
+        <v>5440</v>
       </c>
       <c r="D4" t="n">
-        <v>8186</v>
+        <v>7361</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1539</v>
+        <v>870</v>
       </c>
       <c r="C5" t="n">
-        <v>3934</v>
+        <v>7672</v>
       </c>
       <c r="D5" t="n">
-        <v>2770</v>
+        <v>3765</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>494</v>
       </c>
       <c r="C6" t="n">
-        <v>3171</v>
+        <v>7410</v>
       </c>
       <c r="D6" t="n">
-        <v>871</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>335</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>2558</v>
+        <v>4055</v>
       </c>
       <c r="D7" t="n">
-        <v>508</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1488</v>
+        <v>1315</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>573</v>
+        <v>447</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5092</v>
+        <v>738</v>
       </c>
       <c r="C2" t="n">
-        <v>10597</v>
+        <v>8328</v>
       </c>
       <c r="D2" t="n">
-        <v>14259</v>
+        <v>15866</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4131</v>
+        <v>594</v>
       </c>
       <c r="C3" t="n">
-        <v>3806</v>
+        <v>3345</v>
       </c>
       <c r="D3" t="n">
-        <v>13239</v>
+        <v>8560</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3232</v>
+        <v>741</v>
       </c>
       <c r="C4" t="n">
-        <v>5963</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>9021</v>
+        <v>7450</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1823</v>
+        <v>816</v>
       </c>
       <c r="C5" t="n">
-        <v>4956</v>
+        <v>6505</v>
       </c>
       <c r="D5" t="n">
-        <v>3569</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1111</v>
+        <v>591</v>
       </c>
       <c r="C6" t="n">
-        <v>3521</v>
+        <v>7453</v>
       </c>
       <c r="D6" t="n">
-        <v>1151</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>505</v>
+        <v>237</v>
       </c>
       <c r="C7" t="n">
-        <v>2852</v>
+        <v>5506</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>1942</v>
+        <v>2401</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>928</v>
+        <v>765</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>366</v>
+        <v>305</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2989</v>
+        <v>501</v>
       </c>
       <c r="C2" t="n">
-        <v>4898</v>
+        <v>4397</v>
       </c>
       <c r="D2" t="n">
-        <v>9836</v>
+        <v>11551</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4213</v>
+        <v>809</v>
       </c>
       <c r="C3" t="n">
-        <v>5983</v>
+        <v>4962</v>
       </c>
       <c r="D3" t="n">
-        <v>13035</v>
+        <v>9717</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3601</v>
+        <v>1117</v>
       </c>
       <c r="C4" t="n">
-        <v>5723</v>
+        <v>6722</v>
       </c>
       <c r="D4" t="n">
-        <v>9584</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1929</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>5879</v>
+        <v>10047</v>
       </c>
       <c r="D5" t="n">
-        <v>3885</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>928</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>4512</v>
+        <v>7148</v>
       </c>
       <c r="D6" t="n">
-        <v>1145</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>156</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>3222</v>
+        <v>2352</v>
       </c>
       <c r="D7" t="n">
-        <v>565</v>
+        <v>594</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="C8" t="n">
-        <v>1518</v>
+        <v>749</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3991</v>
+        <v>304</v>
       </c>
       <c r="C2" t="n">
-        <v>8070</v>
+        <v>3258</v>
       </c>
       <c r="D2" t="n">
-        <v>10474</v>
+        <v>8580</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3122</v>
+        <v>579</v>
       </c>
       <c r="C3" t="n">
-        <v>4851</v>
+        <v>4137</v>
       </c>
       <c r="D3" t="n">
-        <v>11802</v>
+        <v>9284</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3404</v>
+        <v>804</v>
       </c>
       <c r="C4" t="n">
-        <v>5786</v>
+        <v>5477</v>
       </c>
       <c r="D4" t="n">
-        <v>9855</v>
+        <v>7507</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2329</v>
+        <v>574</v>
       </c>
       <c r="C5" t="n">
-        <v>5741</v>
+        <v>7534</v>
       </c>
       <c r="D5" t="n">
-        <v>4642</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1205</v>
+        <v>212</v>
       </c>
       <c r="C6" t="n">
-        <v>5104</v>
+        <v>6941</v>
       </c>
       <c r="D6" t="n">
-        <v>1535</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>3814</v>
+        <v>3122</v>
       </c>
       <c r="D7" t="n">
-        <v>633</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2181</v>
+        <v>872</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>754</v>
+        <v>280</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>138</v>
+        <v>76</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2755</v>
+        <v>244</v>
       </c>
       <c r="C2" t="n">
-        <v>4174</v>
+        <v>12080</v>
       </c>
       <c r="D2" t="n">
-        <v>7461</v>
+        <v>13701</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2990</v>
+        <v>378</v>
       </c>
       <c r="C3" t="n">
-        <v>5642</v>
+        <v>3179</v>
       </c>
       <c r="D3" t="n">
-        <v>11084</v>
+        <v>8592</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3055</v>
+        <v>608</v>
       </c>
       <c r="C4" t="n">
-        <v>5437</v>
+        <v>4669</v>
       </c>
       <c r="D4" t="n">
-        <v>9911</v>
+        <v>7530</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2546</v>
+        <v>615</v>
       </c>
       <c r="C5" t="n">
-        <v>5803</v>
+        <v>6291</v>
       </c>
       <c r="D5" t="n">
-        <v>5190</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1415</v>
+        <v>342</v>
       </c>
       <c r="C6" t="n">
-        <v>5575</v>
+        <v>7234</v>
       </c>
       <c r="D6" t="n">
-        <v>1815</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>340</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>4365</v>
+        <v>4992</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>730</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2704</v>
+        <v>1938</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>892</v>
+        <v>543</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>96</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>135</v>
       </c>
       <c r="C2" t="n">
-        <v>6812</v>
+        <v>13194</v>
       </c>
       <c r="D2" t="n">
-        <v>8653</v>
+        <v>13506</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2442</v>
+        <v>266</v>
       </c>
       <c r="C3" t="n">
-        <v>4460</v>
+        <v>6556</v>
       </c>
       <c r="D3" t="n">
-        <v>9999</v>
+        <v>8736</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2634</v>
+        <v>442</v>
       </c>
       <c r="C4" t="n">
-        <v>5414</v>
+        <v>3813</v>
       </c>
       <c r="D4" t="n">
-        <v>9683</v>
+        <v>7484</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2510</v>
+        <v>558</v>
       </c>
       <c r="C5" t="n">
-        <v>5527</v>
+        <v>5366</v>
       </c>
       <c r="D5" t="n">
-        <v>5712</v>
+        <v>4854</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1668</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>5617</v>
+        <v>6716</v>
       </c>
       <c r="D6" t="n">
-        <v>2245</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>624</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>4880</v>
+        <v>6022</v>
       </c>
       <c r="D7" t="n">
-        <v>840</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>3305</v>
+        <v>3284</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>1521</v>
+        <v>1130</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>452</v>
+        <v>333</v>
       </c>
       <c r="D10" t="n">
-        <v>192</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5736</v>
+        <v>3154</v>
       </c>
       <c r="C2" t="n">
-        <v>13522</v>
+        <v>11896</v>
       </c>
       <c r="D2" t="n">
-        <v>6178</v>
+        <v>15062</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2617</v>
+        <v>211</v>
       </c>
       <c r="C2" t="n">
-        <v>3814</v>
+        <v>13186</v>
       </c>
       <c r="D2" t="n">
-        <v>6368</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3243</v>
+        <v>180</v>
       </c>
       <c r="C3" t="n">
-        <v>5402</v>
+        <v>8296</v>
       </c>
       <c r="D3" t="n">
-        <v>10710</v>
+        <v>8773</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3662</v>
+        <v>321</v>
       </c>
       <c r="C4" t="n">
-        <v>7356</v>
+        <v>4934</v>
       </c>
       <c r="D4" t="n">
-        <v>10053</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1634</v>
+        <v>473</v>
       </c>
       <c r="C5" t="n">
-        <v>7954</v>
+        <v>4568</v>
       </c>
       <c r="D5" t="n">
-        <v>5267</v>
+        <v>5038</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>576</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>5993</v>
+        <v>6083</v>
       </c>
       <c r="D6" t="n">
-        <v>1808</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>112</v>
+        <v>248</v>
       </c>
       <c r="C7" t="n">
-        <v>3238</v>
+        <v>6246</v>
       </c>
       <c r="D7" t="n">
-        <v>557</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>1490</v>
+        <v>4382</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>442</v>
+        <v>1941</v>
       </c>
       <c r="D9" t="n">
-        <v>188</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>629</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>203</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6732</v>
+        <v>3800</v>
       </c>
       <c r="C2" t="n">
-        <v>6729</v>
+        <v>8286</v>
       </c>
       <c r="D2" t="n">
-        <v>13789</v>
+        <v>21802</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2437</v>
+        <v>1019</v>
       </c>
       <c r="C3" t="n">
-        <v>6815</v>
+        <v>4697</v>
       </c>
       <c r="D3" t="n">
-        <v>1677</v>
+        <v>2666</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5880</v>
+        <v>2219</v>
       </c>
       <c r="C2" t="n">
-        <v>8416</v>
+        <v>5733</v>
       </c>
       <c r="D2" t="n">
-        <v>12201</v>
+        <v>17212</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3764</v>
+        <v>2040</v>
       </c>
       <c r="C3" t="n">
-        <v>5835</v>
+        <v>5886</v>
       </c>
       <c r="D3" t="n">
-        <v>3588</v>
+        <v>5833</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1093</v>
+        <v>498</v>
       </c>
       <c r="C4" t="n">
-        <v>4036</v>
+        <v>2978</v>
       </c>
       <c r="D4" t="n">
-        <v>1519</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6394</v>
+        <v>2094</v>
       </c>
       <c r="C2" t="n">
-        <v>4562</v>
+        <v>8988</v>
       </c>
       <c r="D2" t="n">
-        <v>14665</v>
+        <v>14010</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3940</v>
+        <v>1757</v>
       </c>
       <c r="C3" t="n">
-        <v>6257</v>
+        <v>4990</v>
       </c>
       <c r="D3" t="n">
-        <v>4707</v>
+        <v>7315</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2064</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>4914</v>
+        <v>4646</v>
       </c>
       <c r="D4" t="n">
-        <v>1870</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="C5" t="n">
-        <v>2304</v>
+        <v>1800</v>
       </c>
       <c r="D5" t="n">
-        <v>1208</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6050</v>
+        <v>1969</v>
       </c>
       <c r="C2" t="n">
-        <v>2812</v>
+        <v>5334</v>
       </c>
       <c r="D2" t="n">
-        <v>20410</v>
+        <v>14125</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4165</v>
+        <v>1584</v>
       </c>
       <c r="C3" t="n">
-        <v>4710</v>
+        <v>6206</v>
       </c>
       <c r="D3" t="n">
-        <v>5889</v>
+        <v>7859</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2511</v>
+        <v>1227</v>
       </c>
       <c r="C4" t="n">
-        <v>5473</v>
+        <v>4744</v>
       </c>
       <c r="D4" t="n">
-        <v>2330</v>
+        <v>3309</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1054</v>
+        <v>585</v>
       </c>
       <c r="C5" t="n">
-        <v>3609</v>
+        <v>3319</v>
       </c>
       <c r="D5" t="n">
-        <v>1274</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>277</v>
+        <v>167</v>
       </c>
       <c r="C6" t="n">
-        <v>1299</v>
+        <v>1068</v>
       </c>
       <c r="D6" t="n">
-        <v>947</v>
+        <v>842</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>352</v>
+        <v>294</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6569</v>
+        <v>1720</v>
       </c>
       <c r="C2" t="n">
-        <v>5305</v>
+        <v>11641</v>
       </c>
       <c r="D2" t="n">
-        <v>23762</v>
+        <v>15337</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3725</v>
+        <v>1455</v>
       </c>
       <c r="C3" t="n">
-        <v>3081</v>
+        <v>5011</v>
       </c>
       <c r="D3" t="n">
-        <v>7226</v>
+        <v>8258</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2041</v>
+        <v>1209</v>
       </c>
       <c r="C4" t="n">
-        <v>4097</v>
+        <v>5431</v>
       </c>
       <c r="D4" t="n">
-        <v>2536</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>917</v>
+        <v>773</v>
       </c>
       <c r="C5" t="n">
-        <v>3339</v>
+        <v>3956</v>
       </c>
       <c r="D5" t="n">
-        <v>1138</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>1643</v>
+        <v>2201</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>912</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C7" t="n">
-        <v>511</v>
+        <v>680</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>275</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5212</v>
+        <v>1540</v>
       </c>
       <c r="C2" t="n">
-        <v>3381</v>
+        <v>12336</v>
       </c>
       <c r="D2" t="n">
-        <v>30418</v>
+        <v>24199</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4256</v>
+        <v>1299</v>
       </c>
       <c r="C3" t="n">
-        <v>3768</v>
+        <v>7196</v>
       </c>
       <c r="D3" t="n">
-        <v>9472</v>
+        <v>8709</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2502</v>
+        <v>1132</v>
       </c>
       <c r="C4" t="n">
-        <v>3397</v>
+        <v>5104</v>
       </c>
       <c r="D4" t="n">
-        <v>3380</v>
+        <v>4644</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1318</v>
+        <v>864</v>
       </c>
       <c r="C5" t="n">
-        <v>3713</v>
+        <v>4595</v>
       </c>
       <c r="D5" t="n">
-        <v>1385</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>568</v>
+        <v>474</v>
       </c>
       <c r="C6" t="n">
-        <v>2583</v>
+        <v>2982</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="C7" t="n">
-        <v>1143</v>
+        <v>1395</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>650</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>471</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>282</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5294</v>
+        <v>1442</v>
       </c>
       <c r="C2" t="n">
-        <v>3952</v>
+        <v>7598</v>
       </c>
       <c r="D2" t="n">
-        <v>26531</v>
+        <v>18945</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3892</v>
+        <v>1860</v>
       </c>
       <c r="C3" t="n">
-        <v>3088</v>
+        <v>10892</v>
       </c>
       <c r="D3" t="n">
-        <v>12141</v>
+        <v>10067</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2906</v>
+        <v>798</v>
       </c>
       <c r="C4" t="n">
-        <v>3500</v>
+        <v>7596</v>
       </c>
       <c r="D4" t="n">
-        <v>4446</v>
+        <v>4451</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1659</v>
+        <v>437</v>
       </c>
       <c r="C5" t="n">
-        <v>3462</v>
+        <v>2922</v>
       </c>
       <c r="D5" t="n">
-        <v>1693</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>854</v>
+        <v>175</v>
       </c>
       <c r="C6" t="n">
-        <v>3150</v>
+        <v>1367</v>
       </c>
       <c r="D6" t="n">
-        <v>914</v>
+        <v>637</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>326</v>
+        <v>88</v>
       </c>
       <c r="C7" t="n">
-        <v>1890</v>
+        <v>461</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>456</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>755</v>
+        <v>276</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>290</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
         <v>202</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
